--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_maule.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:28</t>
+    <t xml:space="preserve">2026-09-24 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -973,7 +973,7 @@
         <v>-0.42</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.04</v>
@@ -996,7 +996,7 @@
         <v>-0.35</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.35</v>
@@ -1019,7 +1019,7 @@
         <v>-0.27</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.11</v>
@@ -1039,13 +1039,13 @@
         <v>30</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="23">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_maule.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:18</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_maule.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
